--- a/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules et papa sont au parc. L'herbe est douce. Papa pose deux sacs. Il dit : voici l'espace du jeu. Jules reste dans l'espace du jeu. Papa donne le ballon. Jules le sent. Il est un peu lourd. Papa dit : on va passer le ballon. Chacun a son tour. Jules passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Jules attend. Puis c'est son tour. Jules passe encore. Un oiseau chante. Jules reste dans l'espace. Il attend. Il passe. Papa dit : bien joué.</t>
+          <t>Jules et papa sont au parc. L'herbe est douce. Papa pose deux sacs. Voici l'espace du jeu. Jules reste dans l'espace du jeu. Papa donne le ballon. Jules le sent. Il est un peu lourd. On va passer le ballon. Chacun a son tour. Jules passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Jules attend. Puis c'est son tour. Jules passe encore. Un oiseau chante. Jules reste dans l'espace. Il attend. Il passe. Bien joué.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules et papa sont au parc. L'herbe est douce. Papa pose deux sacs.
+narrateur|Voici l'espace du jeu.
+narrateur|Jules reste dans l'espace du jeu. Papa donne le ballon. Jules le sent. Il est un peu lourd.
+papa|On va passer le ballon. Chacun a son tour.
+narrateur|Jules passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Jules attend. Puis c'est son tour. Jules passe encore. Un oiseau chante. Jules reste dans l'espace. Il attend. Il passe.
+papa|Bien joué.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a le ballon. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa range le ballon. Jules boit de l'eau. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,11 @@
 papa|Bien joué.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1508,7 @@
           <t>narrateur|Jules a le ballon. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1680,7 @@
           <t>narrateur|Jules a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1844,7 @@
           <t>narrateur|Papa range le ballon. Jules boit de l'eau. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules passe le ballon</t>
+          <t>Amir passe le ballon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un pigeon marche sur le banc mouillé. Amir et papa se passent le ballon dans l'espace du jeu. Maman arrive. Chacun a son tour.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules et papa sont au parc. L'herbe est douce. Papa pose deux sacs. Voici l'espace du jeu. Jules reste dans l'espace du jeu. Papa donne le ballon. Jules le sent. Il est un peu lourd. On va passer le ballon. Chacun a son tour. Jules passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Jules attend. Puis c'est son tour. Jules passe encore. Un oiseau chante. Jules reste dans l'espace. Il attend. Il passe. Bien joué.</t>
+          <t>Un pigeon marche sur le banc mouillé. Ses pattes font des petits bruits. L'herbe brille encore. Elle est douce et froide. Deux sacs reposent près du chemin. Un sac vert. Un sac gris. Maman s'assoit sur le banc sec. Amir, tu vois le pigeon ? Oui, papa. Il marche. Il est sur le banc. Tout doux, le pigeon. En ce moment, papa pose les deux sacs. Voici l'espace du jeu. Amir reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. Il est orange et grainé. Il est lourd. On va passer le ballon. Chacun a son tour. Amir passe le ballon à papa. Papa l'attrape. C'est mon tour. Papa passe le ballon. Amir attend. C'est ton tour. Amir passe encore. Un oiseau chante. Amir reste dans l'espace. Il attend. Il passe. Tu restes dans l'espace. Bien joué. Chacun a son tour. Chacun a son tour. Bravo, Amir. Tu as fait du bon travail. Encore un passage ? Oui, maman. Amir passe le ballon. Papa le rend. Le pigeon s'envole. L'herbe reste douce.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules et papa sont au parc. L'herbe est douce. Papa pose deux sacs.
-narrateur|Voici l'espace du jeu.
-narrateur|Jules reste dans l'espace du jeu. Papa donne le ballon. Jules le sent. Il est un peu lourd.
-papa|On va passer le ballon. Chacun a son tour.
-narrateur|Jules passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Jules attend. Puis c'est son tour. Jules passe encore. Un oiseau chante. Jules reste dans l'espace. Il attend. Il passe.
-papa|Bien joué.</t>
+          <t>narrateur|Un pigeon marche sur le banc mouillé.
+narrateur|Ses pattes font des petits bruits.
+narrateur|L'herbe brille encore.
+narrateur|Elle est douce et froide.
+narrateur|Deux sacs reposent près du chemin.
+narrateur|Un sac vert.
+narrateur|Un sac gris.
+narrateur|Maman s'assoit sur le banc sec.
+papa|Amir, tu vois le pigeon ?
+enfant-m|Oui, papa.
+enfant-m|Il marche.
+papa|Il est sur le banc.
+maman|Tout doux, le pigeon.
+narrateur|En ce moment, papa pose les deux sacs.
+papa|Voici l'espace du jeu.
+narrateur|Amir reste dans l'espace du jeu.
+narrateur|Papa donne le ballon.
+narrateur|Le ballon est un peu lourd.
+narrateur|Il est orange et grainé.
+enfant-m|Il est lourd.
+papa|On va passer le ballon.
+papa|Chacun a son tour.
+narrateur|Amir passe le ballon à papa.
+narrateur|Papa l'attrape.
+papa|C'est mon tour.
+narrateur|Papa passe le ballon.
+narrateur|Amir attend.
+papa|C'est ton tour.
+narrateur|Amir passe encore.
+narrateur|Un oiseau chante.
+narrateur|Amir reste dans l'espace.
+narrateur|Il attend.
+narrateur|Il passe.
+maman|Tu restes dans l'espace.
+papa|Bien joué.
+papa|Chacun a son tour.
+enfant-m|Chacun a son tour.
+papa|Bravo, Amir.
+papa|Tu as fait du bon travail.
+maman|Encore un passage ?
+enfant-m|Oui, maman.
+narrateur|Amir passe le ballon.
+narrateur|Papa le rend.
+narrateur|Le pigeon s'envole.
+narrateur|L'herbe reste douce.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1349,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Jules a le ballon. Que fait-il ?</t>
+          <t>Amir a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1505,10 +1556,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jules a le ballon. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir a le ballon.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
+          <t>Amir a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, papa. Bravo. Chacun a son tour. Tu es resté dans l'espace ? Oui, maman. Bravo. Le ballon orange est un peu froid. L'herbe colle aux chaussures.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1677,10 +1728,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a passé le ballon.
+narrateur|Il a attendu son tour.
+narrateur|Il est resté dans l'espace du jeu.
+papa|Tu as attendu ton tour ?
+enfant-m|Oui, papa.
+papa|Bravo.
+papa|Chacun a son tour.
+maman|Tu es resté dans l'espace ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|Le ballon orange est un peu froid.
+narrateur|L'herbe colle aux chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,7 +1766,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa range le ballon. Jules boit de l'eau. Ils rentrent.</t>
+          <t>Papa range le ballon. Tu bois de l'eau ? Oui, maman. Amir boit de l'eau. La gourde est froide. On rentre ? Oui. Bravo. Ils rentrent. Les sacs tapent tout doux. Le banc est vide, maintenant.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,10 +1902,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa range le ballon. Jules boit de l'eau. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Papa range le ballon.
+maman|Tu bois de l'eau ?
+enfant-m|Oui, maman.
+narrateur|Amir boit de l'eau.
+narrateur|La gourde est froide.
+papa|On rentre ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Ils rentrent.
+narrateur|Les sacs tapent tout doux.
+maman|Le banc est vide, maintenant.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,7 +1939,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le banc est vide. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, papa. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,10 +2079,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le banc est vide.
+papa|Tu as passé le ballon.
+papa|Chacun a son tour.
+maman|Dans l'espace du jeu.
+enfant-m|Oui, papa.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2143,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un pigeon marche sur le banc mouillé. Ses pattes font des petits bruits. L'herbe brille encore. Elle est douce et froide. Deux sacs reposent près du chemin. Un sac vert. Un sac gris. Maman s'assoit sur le banc sec. Amir, tu vois le pigeon ? Oui, papa. Il marche. Il est sur le banc. Tout doux, le pigeon. En ce moment, papa pose les deux sacs. Voici l'espace du jeu. Amir reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. Il est orange et grainé. Il est lourd. On va passer le ballon. Chacun a son tour. Amir passe le ballon à papa. Papa l'attrape. C'est mon tour. Papa passe le ballon. Amir attend. C'est ton tour. Amir passe encore. Un oiseau chante. Amir reste dans l'espace. Il attend. Il passe. Tu restes dans l'espace. Bien joué. Chacun a son tour. Chacun a son tour. Bravo, Amir. Tu as fait du bon travail. Encore un passage ? Oui, maman. Amir passe le ballon. Papa le rend. Le pigeon s'envole. L'herbe reste douce.</t>
+          <t>Un pigeon marche sur le banc mouillé. Ses pattes font des petits bruits. L'herbe brille encore. Elle est douce et froide. Deux sacs reposent près du chemin. Un sac vert. Un sac gris. Une feuille colle au banc. Le chemin est encore humide. Maman s'assoit sur le banc sec. Elle ouvre la gourde. Amir, tu vois le pigeon ? Oui, papa. Il marche. Il est sur le banc. Tout doux, le pigeon. En ce moment, papa pose les deux sacs. Voici l'espace du jeu. Amir reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. Il est orange et grainé. Il est lourd. On va passer le ballon. Chacun a son tour. Amir passe le ballon à papa. Papa l'attrape. C'est mon tour. Papa passe le ballon. Amir attend. C'est ton tour. Amir passe encore. Un oiseau chante. Amir reste dans l'espace. Il attend. Il passe. Tu restes dans l'espace. Bien joué. Chacun a son tour. Chacun a son tour. Bravo, Amir. Encore un passage ? Oui, maman. Amir passe le ballon. Papa le rend. Le pigeon s'envole. L'herbe reste douce. Le banc est sec, maintenant. On reste encore un peu. Oui. Le ballon repose entre les sacs.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules et papa sont au parc. L'herbe est douce. Papa pose deux sacs. Il dit : voici l'espace du jeu. Jules reste dans l'espace du jeu. Papa donne le ballon. Jules le sent. Il est un peu lourd. Papa dit : on va &lt;emphasis level="moderate"&gt;passer&lt;/emphasis&gt; le ballon. Chacun a son tour. Jules passe le ballon à papa. Papa l'attrape. C'est le tour de papa. Papa passe le ballon. Jules attend. Puis c'est son tour. Jules passe encore. Un oiseau chante. Jules reste dans l'espace. Il attend. Il passe. Papa dit : bien joué.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un pigeon marche sur le banc mouillé. Ses pattes font des petits bruits. L'herbe brille encore. Elle est douce et froide. Deux sacs reposent près du chemin. Un sac vert. Un sac gris. Une feuille colle au banc. Le chemin est encore humide. Maman s'assoit sur le banc sec. Elle ouvre la gourde. Amir, tu vois le pigeon ? Oui, papa. Il marche. Il est sur le banc. Tout doux, le pigeon. En ce moment, papa pose les deux sacs. Voici l'espace du jeu. Amir reste dans l'espace du jeu. Papa donne le ballon. Le ballon est un peu lourd. Il est orange et grainé. Il est lourd. On va passer le ballon. Chacun a son tour. Amir passe le ballon à papa. Papa l'attrape. C'est mon tour. Papa passe le ballon. Amir attend. C'est ton tour. Amir passe encore. Un oiseau chante. Amir reste dans l'espace. Il attend. Il passe. Tu restes dans l'espace. Bien joué. Chacun a son tour. Chacun a son tour. Bravo, Amir. Encore un passage ? Oui, maman. Amir passe le ballon. Papa le rend. Le pigeon s'envole. L'herbe reste douce. Le banc est sec, maintenant. On reste encore un peu. Oui. Le ballon repose entre les sacs.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1331,7 +1331,10 @@
 narrateur|Deux sacs reposent près du chemin.
 narrateur|Un sac vert.
 narrateur|Un sac gris.
+narrateur|Une feuille colle au banc.
+narrateur|Le chemin est encore humide.
 narrateur|Maman s'assoit sur le banc sec.
+narrateur|Elle ouvre la gourde.
 papa|Amir, tu vois le pigeon ?
 enfant-m|Oui, papa.
 enfant-m|Il marche.
@@ -1362,13 +1365,16 @@
 papa|Chacun a son tour.
 enfant-m|Chacun a son tour.
 papa|Bravo, Amir.
-papa|Tu as fait du bon travail.
 maman|Encore un passage ?
 enfant-m|Oui, maman.
 narrateur|Amir passe le ballon.
 narrateur|Papa le rend.
 narrateur|Le pigeon s'envole.
-narrateur|L'herbe reste douce.</t>
+narrateur|L'herbe reste douce.
+maman|Le banc est sec, maintenant.
+papa|On reste encore un peu.
+enfant-m|Oui.
+narrateur|Le ballon repose entre les sacs.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1405,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules a le ballon. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a le ballon. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, papa. Bravo. Chacun a son tour. Tu es resté dans l'espace ? Oui, maman. Bravo. Le ballon orange est un peu froid. L'herbe colle aux chaussures.</t>
+          <t>Amir a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, papa. Bravo. Chacun a son tour. Tu es resté dans l'espace ? Oui, maman. Bravo. Le ballon orange est un peu froid. L'herbe colle aux chaussures. On reprend un tour ? Oui, papa. Amir attend. Puis il passe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Jules a passé le ballon. Il a attendu son &lt;emphasis level="moderate"&gt;tour&lt;/emphasis&gt;. Il est resté dans l'espace du jeu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a passé le ballon. Il a attendu son tour. Il est resté dans l'espace du jeu. Tu as attendu ton tour ? Oui, papa. Bravo. Chacun a son tour. Tu es resté dans l'espace ? Oui, maman. Bravo. Le ballon orange est un peu froid. L'herbe colle aux chaussures. On reprend un tour ? Oui, papa. Amir attend. Puis il passe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1739,7 +1745,11 @@
 enfant-m|Oui, maman.
 maman|Bravo.
 narrateur|Le ballon orange est un peu froid.
-narrateur|L'herbe colle aux chaussures.</t>
+narrateur|L'herbe colle aux chaussures.
+papa|On reprend un tour ?
+enfant-m|Oui, papa.
+narrateur|Amir attend.
+narrateur|Puis il passe.</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Papa range le ballon. Jules boit de l'eau. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa range le ballon. Tu bois de l'eau ? Oui, maman. Amir boit de l'eau. La gourde est froide. On rentre ? Oui. Bravo. Ils rentrent. Les sacs tapent tout doux. Le banc est vide, maintenant.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le banc est vide. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, papa. L'histoire est finie.</t>
+          <t>Le banc est vide. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, papa.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le banc est vide. Tu as passé le ballon. Chacun a son tour. Dans l'espace du jeu. Oui, papa.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2083,8 +2093,7 @@
 papa|Tu as passé le ballon.
 papa|Chacun a son tour.
 maman|Dans l'espace du jeu.
-enfant-m|Oui, papa.
-narrateur|L'histoire est finie.</t>
+enfant-m|Oui, papa.</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2150,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
+++ b/stories/arbres/ATOM-JEU.BAL.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>parc</t>
+          <t>parc, banc mouillé, herbe, deux sacs</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, papa</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
